--- a/Accommodation.xlsx
+++ b/Accommodation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssefawad/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssefawad/Downloads/kings-accommodation-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED4C26C-CA51-4947-9B1B-437D75BEE3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D3DC3D-085E-9A4A-B94C-2F392B8529AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14880" yWindow="760" windowWidth="19680" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14880" yWindow="760" windowWidth="19680" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="130">
   <si>
     <t>Accommodation Type</t>
   </si>
@@ -53,10 +53,6 @@
 Laundry in basement</t>
   </si>
   <si>
-    <t>40 min walk
-17 min central line tube (£2.80)</t>
-  </si>
-  <si>
     <t>Non-ensuite (8 sq m)</t>
   </si>
   <si>
@@ -277,13 +273,173 @@
   </si>
   <si>
     <t>https://www.kcl.ac.uk/accommodation/residences/orchard-lisle-and-iris-brook</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Marleybone</t>
+  </si>
+  <si>
+    <t>Non-ensuite</t>
+  </si>
+  <si>
+    <t>£287</t>
+  </si>
+  <si>
+    <t>Bills+wifi included
+cleaning service once per month</t>
+  </si>
+  <si>
+    <t>(51.52498, -0.16626)</t>
+  </si>
+  <si>
+    <t>Bills not included</t>
+  </si>
+  <si>
+    <t>Camden</t>
+  </si>
+  <si>
+    <t>(51.54322, -0.13606)</t>
+  </si>
+  <si>
+    <t>£262</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 2 others, balcony</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 3 others, private balcony</t>
+  </si>
+  <si>
+    <t>King's Cross</t>
+  </si>
+  <si>
+    <t>£237</t>
+  </si>
+  <si>
+    <t>(51.53932, -0.11817)</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 3 others, backyard</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17813314</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17804296</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17784470</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>1 hour walk
+35 min Northern (£2.90)</t>
+  </si>
+  <si>
+    <t>40 min walk
+17 min central (£2.80)</t>
+  </si>
+  <si>
+    <t>1 hour walk
+28 min Bakerloo (£2.80)</t>
+  </si>
+  <si>
+    <t>50 min walk
+36 min bus (£1.75)</t>
+  </si>
+  <si>
+    <t>£247</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 2 others</t>
+  </si>
+  <si>
+    <t>(51.531681,-0.109451)</t>
+  </si>
+  <si>
+    <t>40 min walk
+26 min bus (£1.75)</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17810431</t>
+  </si>
+  <si>
+    <t>Old Street</t>
+  </si>
+  <si>
+    <t>£212</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17289836</t>
+  </si>
+  <si>
+    <t>(51.528405, -0.08311)</t>
+  </si>
+  <si>
+    <t>50 min walk
+37 min bus (£1.75)</t>
+  </si>
+  <si>
+    <t>Elephant &amp; Castle</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 2 others, backyard</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/15630344</t>
+  </si>
+  <si>
+    <t>(51.490823,-0.101226)</t>
+  </si>
+  <si>
+    <t>46 min walk
+26 min Northern (£2.90)</t>
+  </si>
+  <si>
+    <t>£250</t>
+  </si>
+  <si>
+    <t>Share flat/bath with 1 other</t>
+  </si>
+  <si>
+    <t>(51.49266, -0.09179)</t>
+  </si>
+  <si>
+    <t>48 min walk
+23 min bus (£1.75)</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17792477</t>
+  </si>
+  <si>
+    <t>Bermondsey</t>
+  </si>
+  <si>
+    <t>Ensuite</t>
+  </si>
+  <si>
+    <t>Share flat with 3 others, backyard</t>
+  </si>
+  <si>
+    <t>(51.49619, -0.06377)</t>
+  </si>
+  <si>
+    <t>1 hour walk
+25 min tube (£3.50)</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/16759440</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -310,6 +466,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -319,7 +482,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -490,12 +653,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -556,6 +732,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -675,7 +862,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:I20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:I23">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Accommodation Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Features"/>
@@ -892,13 +1079,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="2" max="2" width="45.5" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
     <col min="6" max="6" width="19.1640625" customWidth="1"/>
     <col min="7" max="7" width="40.1640625" customWidth="1"/>
@@ -929,10 +1116,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="56">
@@ -943,25 +1130,25 @@
         <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
@@ -970,19 +1157,19 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="H3" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
@@ -991,44 +1178,44 @@
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
@@ -1037,19 +1224,19 @@
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="H6" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
@@ -1058,48 +1245,48 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>34</v>
-      </c>
       <c r="H8" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
@@ -1108,44 +1295,44 @@
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="H10" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
@@ -1154,19 +1341,19 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="H11" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
@@ -1175,150 +1362,313 @@
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>47</v>
-      </c>
       <c r="G13" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="H14" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="G15" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="H15" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28">
+      <c r="A16" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28">
       <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28">
       <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28">
       <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28">
       <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28">
+      <c r="A21" s="22"/>
+      <c r="B21" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28">
+      <c r="A22" s="22"/>
+      <c r="B22" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28">
+      <c r="A23" s="22"/>
+      <c r="B23" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>129</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1336,10 +1686,18 @@
     <hyperlink ref="I13" r:id="rId12" xr:uid="{F854A460-4395-8741-B349-EBAA30585B8F}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{53C90DC4-E228-1943-A33B-C730FB1F2F87}"/>
     <hyperlink ref="I15" r:id="rId14" xr:uid="{B607297E-2E00-2D4C-9BF2-50C4CF403DB5}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{F5AEA932-5BEC-5747-BBC4-EF829E5E3B6B}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{C7925D95-702D-0547-9F7D-F3C46BCD6F83}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{B5270A47-BA46-3D40-B2C5-ED330419A15A}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{42F44A36-653C-964E-A685-2C077CA02AD3}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{5D006489-008B-D34C-8D53-2C4AA998730A}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{0F27B2F8-42FA-F840-8748-3A465B45899B}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{85B78589-4FEE-8742-8D05-D1C0DD5267F7}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{8F6DBF24-1CE5-354D-B4A9-DD4065C66EF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Accommodation.xlsx
+++ b/Accommodation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssefawad/Downloads/kings-accommodation-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D3DC3D-085E-9A4A-B94C-2F392B8529AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548547E2-166C-224D-9C35-83544E31F861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14880" yWindow="760" windowWidth="19680" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,15 +324,6 @@
     <t>Share flat/bath with 3 others, backyard</t>
   </si>
   <si>
-    <t>https://www.spareroom.co.uk/17813314</t>
-  </si>
-  <si>
-    <t>https://www.spareroom.co.uk/17804296</t>
-  </si>
-  <si>
-    <t>https://www.spareroom.co.uk/17784470</t>
-  </si>
-  <si>
     <t>Angel</t>
   </si>
   <si>
@@ -365,16 +356,10 @@
 26 min bus (£1.75)</t>
   </si>
   <si>
-    <t>https://www.spareroom.co.uk/17810431</t>
-  </si>
-  <si>
     <t>Old Street</t>
   </si>
   <si>
     <t>£212</t>
-  </si>
-  <si>
-    <t>https://www.spareroom.co.uk/17289836</t>
   </si>
   <si>
     <t>(51.528405, -0.08311)</t>
@@ -390,9 +375,6 @@
     <t>Share flat/bath with 2 others, backyard</t>
   </si>
   <si>
-    <t>https://www.spareroom.co.uk/15630344</t>
-  </si>
-  <si>
     <t>(51.490823,-0.101226)</t>
   </si>
   <si>
@@ -413,9 +395,6 @@
 23 min bus (£1.75)</t>
   </si>
   <si>
-    <t>https://www.spareroom.co.uk/17792477</t>
-  </si>
-  <si>
     <t>Bermondsey</t>
   </si>
   <si>
@@ -432,7 +411,28 @@
 25 min tube (£3.50)</t>
   </si>
   <si>
-    <t>https://www.spareroom.co.uk/16759440</t>
+    <t>spareroom://advert?id=17813314</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=17804296</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=17784470</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=17810431</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=17289836</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=15630344</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=17792477</t>
+  </si>
+  <si>
+    <t>spareroom://advert?id=16759440</t>
   </si>
 </sst>
 </file>
@@ -671,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -736,12 +736,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1133,7 +1132,7 @@
         <v>56</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>9</v>
@@ -1452,7 +1451,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="28">
+    <row r="16" spans="1:9" ht="42">
       <c r="A16" s="4" t="s">
         <v>80</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>81</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>82</v>
@@ -1478,7 +1477,7 @@
         <v>85</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="28">
@@ -1490,7 +1489,7 @@
         <v>87</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>82</v>
@@ -1505,7 +1504,7 @@
         <v>88</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28">
@@ -1517,7 +1516,7 @@
         <v>92</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>82</v>
@@ -1532,7 +1531,7 @@
         <v>94</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28">
@@ -1541,25 +1540,25 @@
         <v>84</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28">
@@ -1568,103 +1567,100 @@
         <v>86</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28">
+      <c r="B21" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="28">
-      <c r="A21" s="22"/>
-      <c r="B21" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="22" t="s">
         <v>82</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28">
+      <c r="B22" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="I22" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28">
+      <c r="B23" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="28">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22" s="24" t="s">
+      <c r="D23" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="28">
-      <c r="A23" s="22"/>
-      <c r="B23" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>125</v>
+      <c r="E23" s="22" t="s">
+        <v>118</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>127</v>
+      <c r="G23" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>120</v>
       </c>
       <c r="I23" s="21" t="s">
         <v>129</v>
@@ -1686,14 +1682,14 @@
     <hyperlink ref="I13" r:id="rId12" xr:uid="{F854A460-4395-8741-B349-EBAA30585B8F}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{53C90DC4-E228-1943-A33B-C730FB1F2F87}"/>
     <hyperlink ref="I15" r:id="rId14" xr:uid="{B607297E-2E00-2D4C-9BF2-50C4CF403DB5}"/>
-    <hyperlink ref="I16" r:id="rId15" xr:uid="{F5AEA932-5BEC-5747-BBC4-EF829E5E3B6B}"/>
-    <hyperlink ref="I17" r:id="rId16" xr:uid="{C7925D95-702D-0547-9F7D-F3C46BCD6F83}"/>
-    <hyperlink ref="I18" r:id="rId17" xr:uid="{B5270A47-BA46-3D40-B2C5-ED330419A15A}"/>
-    <hyperlink ref="I19" r:id="rId18" xr:uid="{42F44A36-653C-964E-A685-2C077CA02AD3}"/>
-    <hyperlink ref="I20" r:id="rId19" xr:uid="{5D006489-008B-D34C-8D53-2C4AA998730A}"/>
-    <hyperlink ref="I21" r:id="rId20" xr:uid="{0F27B2F8-42FA-F840-8748-3A465B45899B}"/>
-    <hyperlink ref="I22" r:id="rId21" xr:uid="{85B78589-4FEE-8742-8D05-D1C0DD5267F7}"/>
-    <hyperlink ref="I23" r:id="rId22" xr:uid="{8F6DBF24-1CE5-354D-B4A9-DD4065C66EF6}"/>
+    <hyperlink ref="I16" r:id="rId15" display="https://www.spareroom.co.uk/17813314" xr:uid="{F5AEA932-5BEC-5747-BBC4-EF829E5E3B6B}"/>
+    <hyperlink ref="I17" r:id="rId16" display="https://www.spareroom.co.uk/17804296" xr:uid="{C7925D95-702D-0547-9F7D-F3C46BCD6F83}"/>
+    <hyperlink ref="I18" r:id="rId17" display="https://www.spareroom.co.uk/17784470" xr:uid="{B5270A47-BA46-3D40-B2C5-ED330419A15A}"/>
+    <hyperlink ref="I19" r:id="rId18" display="https://www.spareroom.co.uk/17810431" xr:uid="{42F44A36-653C-964E-A685-2C077CA02AD3}"/>
+    <hyperlink ref="I20" r:id="rId19" display="https://www.spareroom.co.uk/17289836" xr:uid="{5D006489-008B-D34C-8D53-2C4AA998730A}"/>
+    <hyperlink ref="I21" r:id="rId20" display="https://www.spareroom.co.uk/15630344" xr:uid="{0F27B2F8-42FA-F840-8748-3A465B45899B}"/>
+    <hyperlink ref="I22" r:id="rId21" display="https://www.spareroom.co.uk/17792477" xr:uid="{85B78589-4FEE-8742-8D05-D1C0DD5267F7}"/>
+    <hyperlink ref="I23" r:id="rId22" display="https://www.spareroom.co.uk/16759440" xr:uid="{8F6DBF24-1CE5-354D-B4A9-DD4065C66EF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Accommodation.xlsx
+++ b/Accommodation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssefawad/Downloads/kings-accommodation-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548547E2-166C-224D-9C35-83544E31F861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3642362-BBF9-5D4C-9F28-247FE0D281B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14880" yWindow="760" windowWidth="19680" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="132">
   <si>
     <t>Accommodation Type</t>
   </si>
@@ -433,6 +433,12 @@
   </si>
   <si>
     <t>spareroom://advert?id=16759440</t>
+  </si>
+  <si>
+    <t>https://www.spareroom.co.uk/17813314</t>
+  </si>
+  <si>
+    <t>app</t>
   </si>
 </sst>
 </file>
@@ -474,12 +480,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -671,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -733,15 +751,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -861,8 +883,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:I23">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A1:J23">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Accommodation Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Features"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Location"/>
@@ -872,6 +894,7 @@
     <tableColumn id="9" xr3:uid="{26B55097-B8A4-A345-AC25-785B4C59B79A}" name="Details" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{CCF74B2C-5F3B-BD43-9775-F42D479CF363}" name="loc" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="site"/>
+    <tableColumn id="10" xr3:uid="{552B7942-3171-C440-957A-3776FA7E67A6}" name="app"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1078,7 +1101,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
@@ -1090,9 +1113,10 @@
     <col min="7" max="7" width="40.1640625" customWidth="1"/>
     <col min="8" max="8" width="19.83203125" customWidth="1"/>
     <col min="9" max="9" width="59.83203125" customWidth="1"/>
+    <col min="10" max="10" width="27.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,8 +1144,11 @@
       <c r="I1" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="56">
+      <c r="J1" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="56">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -1150,7 +1177,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -1171,7 +1198,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
@@ -1192,7 +1219,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="8" t="s">
@@ -1217,7 +1244,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -1238,7 +1265,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1259,7 +1286,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -1288,7 +1315,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
@@ -1309,7 +1336,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="10" t="s">
@@ -1334,7 +1361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1355,7 +1382,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -1376,7 +1403,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="11" t="s">
@@ -1401,7 +1428,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="12" t="s">
@@ -1426,7 +1453,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="11" t="s">
@@ -1451,7 +1478,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="42">
+    <row r="16" spans="1:10" ht="42">
       <c r="A16" s="4" t="s">
         <v>80</v>
       </c>
@@ -1476,11 +1503,14 @@
       <c r="H16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="25" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28">
+    <row r="17" spans="1:10" ht="28">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>86</v>
@@ -1503,11 +1533,14 @@
       <c r="H17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="28">
+    <row r="18" spans="1:10" ht="28">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>86</v>
@@ -1530,11 +1563,14 @@
       <c r="H18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="21" t="s">
+      <c r="I18" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J18" s="25" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="28">
+    <row r="19" spans="1:10" ht="28">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>84</v>
@@ -1557,11 +1593,14 @@
       <c r="H19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J19" s="26" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28">
+    <row r="20" spans="1:10" ht="28">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>86</v>
@@ -1584,85 +1623,97 @@
       <c r="H20" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J20" s="25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28">
-      <c r="B21" s="24" t="s">
+    <row r="21" spans="1:10" ht="28">
+      <c r="B21" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="21" t="s">
         <v>82</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28">
-      <c r="B22" s="22" t="s">
+    <row r="22" spans="1:10" ht="28">
+      <c r="B22" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" s="25" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="28">
-      <c r="B23" s="22" t="s">
+    <row r="23" spans="1:10" ht="28">
+      <c r="B23" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="21" t="s">
         <v>118</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" s="26" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1682,18 +1733,26 @@
     <hyperlink ref="I13" r:id="rId12" xr:uid="{F854A460-4395-8741-B349-EBAA30585B8F}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{53C90DC4-E228-1943-A33B-C730FB1F2F87}"/>
     <hyperlink ref="I15" r:id="rId14" xr:uid="{B607297E-2E00-2D4C-9BF2-50C4CF403DB5}"/>
-    <hyperlink ref="I16" r:id="rId15" display="https://www.spareroom.co.uk/17813314" xr:uid="{F5AEA932-5BEC-5747-BBC4-EF829E5E3B6B}"/>
-    <hyperlink ref="I17" r:id="rId16" display="https://www.spareroom.co.uk/17804296" xr:uid="{C7925D95-702D-0547-9F7D-F3C46BCD6F83}"/>
-    <hyperlink ref="I18" r:id="rId17" display="https://www.spareroom.co.uk/17784470" xr:uid="{B5270A47-BA46-3D40-B2C5-ED330419A15A}"/>
-    <hyperlink ref="I19" r:id="rId18" display="https://www.spareroom.co.uk/17810431" xr:uid="{42F44A36-653C-964E-A685-2C077CA02AD3}"/>
-    <hyperlink ref="I20" r:id="rId19" display="https://www.spareroom.co.uk/17289836" xr:uid="{5D006489-008B-D34C-8D53-2C4AA998730A}"/>
-    <hyperlink ref="I21" r:id="rId20" display="https://www.spareroom.co.uk/15630344" xr:uid="{0F27B2F8-42FA-F840-8748-3A465B45899B}"/>
-    <hyperlink ref="I22" r:id="rId21" display="https://www.spareroom.co.uk/17792477" xr:uid="{85B78589-4FEE-8742-8D05-D1C0DD5267F7}"/>
-    <hyperlink ref="I23" r:id="rId22" display="https://www.spareroom.co.uk/16759440" xr:uid="{8F6DBF24-1CE5-354D-B4A9-DD4065C66EF6}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{472D7C98-E6C5-3247-9482-12F697F35328}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{E50CA980-C89C-5B4B-A954-5136623E3548}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{D757F707-67A5-6442-8559-2F67F24EF898}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{6DBE2EB6-EE7C-1F47-A991-5AA76FC85F25}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{D092E9A5-C7FB-6D4F-A36A-FD96F9E53C1D}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{C9AAD761-40B7-2345-913D-A8FE5303A61E}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{C88ABA12-49C9-4645-B569-591A760AE7BF}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{E4F351C2-CB53-3641-AF7D-3D23F919325B}"/>
+    <hyperlink ref="J23" r:id="rId23" display="https://www.spareroom.co.uk/16759440" xr:uid="{536C7335-00A9-6147-A493-FD1319E5A560}"/>
+    <hyperlink ref="J22" r:id="rId24" display="https://www.spareroom.co.uk/17792477" xr:uid="{55DAE0D8-F1BB-AF49-9FCF-A28C2DF1FE1F}"/>
+    <hyperlink ref="J21" r:id="rId25" display="https://www.spareroom.co.uk/15630344" xr:uid="{1BFD1D8E-3022-BD48-BF09-EC36249DB66D}"/>
+    <hyperlink ref="J20" r:id="rId26" display="https://www.spareroom.co.uk/17289836" xr:uid="{A995D061-C891-2242-B3CF-0B61C57E1EDF}"/>
+    <hyperlink ref="J19" r:id="rId27" display="https://www.spareroom.co.uk/17810431" xr:uid="{04EACE8B-4401-A445-BD4D-1DDCA2CF10CA}"/>
+    <hyperlink ref="J18" r:id="rId28" display="https://www.spareroom.co.uk/17784470" xr:uid="{73340FB1-2CD0-D142-9B78-F274D1B0D4AA}"/>
+    <hyperlink ref="J17" r:id="rId29" display="https://www.spareroom.co.uk/17804296" xr:uid="{3A39B5E2-17A3-2A4E-AD78-C20D47D9E7E1}"/>
+    <hyperlink ref="J16" r:id="rId30" display="https://www.spareroom.co.uk/17813314" xr:uid="{6CFE71A0-B81B-9C4F-8C19-DF788A31E32D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId23"/>
+    <tablePart r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
